--- a/BWI/bestwine_output/bestwine_Norway.xlsx
+++ b/BWI/bestwine_output/bestwine_Norway.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA430"/>
+  <dimension ref="A1:AA432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -46314,6 +46314,208 @@
         </is>
       </c>
     </row>
+    <row r="431">
+      <c r="A431" s="2" t="inlineStr">
+        <is>
+          <t>Bevhouse As</t>
+        </is>
+      </c>
+      <c r="B431" s="2" t="inlineStr">
+        <is>
+          <t>Bevhouse As</t>
+        </is>
+      </c>
+      <c r="C431" s="2" t="inlineStr">
+        <is>
+          <t>122451</t>
+        </is>
+      </c>
+      <c r="D431" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E431" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F431" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G431" s="2" t="inlineStr">
+        <is>
+          <t>14 Universitetsgata</t>
+        </is>
+      </c>
+      <c r="H431" s="2" t="inlineStr">
+        <is>
+          <t>0164</t>
+        </is>
+      </c>
+      <c r="I431" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bevhouse.no</t>
+        </is>
+      </c>
+      <c r="J431" s="2" t="inlineStr"/>
+      <c r="K431" s="2" t="inlineStr"/>
+      <c r="L431" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M431" s="2" t="inlineStr"/>
+      <c r="N431" s="2" t="inlineStr">
+        <is>
+          <t>post@bevhouse.no</t>
+        </is>
+      </c>
+      <c r="O431" s="2" t="inlineStr"/>
+      <c r="P431" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="Q431" s="2" t="inlineStr">
+        <is>
+          <t>929413393</t>
+        </is>
+      </c>
+      <c r="R431" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bevhouse/?originalSubdomain</t>
+        </is>
+      </c>
+      <c r="S431" s="2" t="inlineStr"/>
+      <c r="T431" s="2" t="inlineStr"/>
+      <c r="U431" s="2" t="inlineStr"/>
+      <c r="V431" s="2" t="inlineStr"/>
+      <c r="W431" s="2" t="inlineStr">
+        <is>
+          <t>Arnstein Nilssen</t>
+        </is>
+      </c>
+      <c r="X431" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder/ Managing Director</t>
+        </is>
+      </c>
+      <c r="Y431" s="2" t="inlineStr"/>
+      <c r="Z431" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA431" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/arnstein-nilssen-851b7731/</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="2" t="inlineStr">
+        <is>
+          <t>Bevhouse As</t>
+        </is>
+      </c>
+      <c r="B432" s="2" t="inlineStr">
+        <is>
+          <t>Bevhouse As</t>
+        </is>
+      </c>
+      <c r="C432" s="2" t="inlineStr">
+        <is>
+          <t>122451</t>
+        </is>
+      </c>
+      <c r="D432" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E432" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F432" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G432" s="2" t="inlineStr">
+        <is>
+          <t>14 Universitetsgata</t>
+        </is>
+      </c>
+      <c r="H432" s="2" t="inlineStr">
+        <is>
+          <t>0164</t>
+        </is>
+      </c>
+      <c r="I432" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bevhouse.no</t>
+        </is>
+      </c>
+      <c r="J432" s="2" t="inlineStr"/>
+      <c r="K432" s="2" t="inlineStr"/>
+      <c r="L432" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M432" s="2" t="inlineStr"/>
+      <c r="N432" s="2" t="inlineStr">
+        <is>
+          <t>post@bevhouse.no</t>
+        </is>
+      </c>
+      <c r="O432" s="2" t="inlineStr"/>
+      <c r="P432" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="Q432" s="2" t="inlineStr">
+        <is>
+          <t>929413393</t>
+        </is>
+      </c>
+      <c r="R432" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bevhouse/?originalSubdomain</t>
+        </is>
+      </c>
+      <c r="S432" s="2" t="inlineStr"/>
+      <c r="T432" s="2" t="inlineStr"/>
+      <c r="U432" s="2" t="inlineStr"/>
+      <c r="V432" s="2" t="inlineStr"/>
+      <c r="W432" s="2" t="inlineStr">
+        <is>
+          <t>Andrée Lind</t>
+        </is>
+      </c>
+      <c r="X432" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y432" s="2" t="inlineStr"/>
+      <c r="Z432" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA432" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/andr%C3%A9e-lind-a0429612b/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Norway.xlsx
+++ b/BWI/bestwine_output/bestwine_Norway.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA432"/>
+  <dimension ref="A1:AA434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -46516,6 +46516,208 @@
         </is>
       </c>
     </row>
+    <row r="433">
+      <c r="A433" s="2" t="inlineStr">
+        <is>
+          <t>Bevhouse As</t>
+        </is>
+      </c>
+      <c r="B433" s="2" t="inlineStr">
+        <is>
+          <t>Bevhouse As</t>
+        </is>
+      </c>
+      <c r="C433" s="2" t="inlineStr">
+        <is>
+          <t>122451</t>
+        </is>
+      </c>
+      <c r="D433" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E433" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F433" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G433" s="2" t="inlineStr">
+        <is>
+          <t>14 Universitetsgata</t>
+        </is>
+      </c>
+      <c r="H433" s="2" t="inlineStr">
+        <is>
+          <t>0164</t>
+        </is>
+      </c>
+      <c r="I433" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bevhouse.no</t>
+        </is>
+      </c>
+      <c r="J433" s="2" t="inlineStr"/>
+      <c r="K433" s="2" t="inlineStr"/>
+      <c r="L433" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M433" s="2" t="inlineStr"/>
+      <c r="N433" s="2" t="inlineStr">
+        <is>
+          <t>post@bevhouse.no</t>
+        </is>
+      </c>
+      <c r="O433" s="2" t="inlineStr"/>
+      <c r="P433" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="Q433" s="2" t="inlineStr">
+        <is>
+          <t>929413393</t>
+        </is>
+      </c>
+      <c r="R433" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bevhouse/?originalSubdomain</t>
+        </is>
+      </c>
+      <c r="S433" s="2" t="inlineStr"/>
+      <c r="T433" s="2" t="inlineStr"/>
+      <c r="U433" s="2" t="inlineStr"/>
+      <c r="V433" s="2" t="inlineStr"/>
+      <c r="W433" s="2" t="inlineStr">
+        <is>
+          <t>Arnstein Nilssen</t>
+        </is>
+      </c>
+      <c r="X433" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder/ Managing Director</t>
+        </is>
+      </c>
+      <c r="Y433" s="2" t="inlineStr"/>
+      <c r="Z433" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA433" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/arnstein-nilssen-851b7731/</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="2" t="inlineStr">
+        <is>
+          <t>Bevhouse As</t>
+        </is>
+      </c>
+      <c r="B434" s="2" t="inlineStr">
+        <is>
+          <t>Bevhouse As</t>
+        </is>
+      </c>
+      <c r="C434" s="2" t="inlineStr">
+        <is>
+          <t>122451</t>
+        </is>
+      </c>
+      <c r="D434" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E434" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F434" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G434" s="2" t="inlineStr">
+        <is>
+          <t>14 Universitetsgata</t>
+        </is>
+      </c>
+      <c r="H434" s="2" t="inlineStr">
+        <is>
+          <t>0164</t>
+        </is>
+      </c>
+      <c r="I434" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bevhouse.no</t>
+        </is>
+      </c>
+      <c r="J434" s="2" t="inlineStr"/>
+      <c r="K434" s="2" t="inlineStr"/>
+      <c r="L434" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M434" s="2" t="inlineStr"/>
+      <c r="N434" s="2" t="inlineStr">
+        <is>
+          <t>post@bevhouse.no</t>
+        </is>
+      </c>
+      <c r="O434" s="2" t="inlineStr"/>
+      <c r="P434" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="Q434" s="2" t="inlineStr">
+        <is>
+          <t>929413393</t>
+        </is>
+      </c>
+      <c r="R434" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bevhouse/?originalSubdomain</t>
+        </is>
+      </c>
+      <c r="S434" s="2" t="inlineStr"/>
+      <c r="T434" s="2" t="inlineStr"/>
+      <c r="U434" s="2" t="inlineStr"/>
+      <c r="V434" s="2" t="inlineStr"/>
+      <c r="W434" s="2" t="inlineStr">
+        <is>
+          <t>Andrée Lind</t>
+        </is>
+      </c>
+      <c r="X434" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y434" s="2" t="inlineStr"/>
+      <c r="Z434" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA434" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/andr%C3%A9e-lind-a0429612b/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Norway.xlsx
+++ b/BWI/bestwine_output/bestwine_Norway.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA434"/>
+  <dimension ref="A1:AA436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -46718,6 +46718,208 @@
         </is>
       </c>
     </row>
+    <row r="435">
+      <c r="A435" s="2" t="inlineStr">
+        <is>
+          <t>Bevhouse As</t>
+        </is>
+      </c>
+      <c r="B435" s="2" t="inlineStr">
+        <is>
+          <t>Bevhouse As</t>
+        </is>
+      </c>
+      <c r="C435" s="2" t="inlineStr">
+        <is>
+          <t>122451</t>
+        </is>
+      </c>
+      <c r="D435" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E435" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F435" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G435" s="2" t="inlineStr">
+        <is>
+          <t>14 Universitetsgata</t>
+        </is>
+      </c>
+      <c r="H435" s="2" t="inlineStr">
+        <is>
+          <t>0164</t>
+        </is>
+      </c>
+      <c r="I435" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bevhouse.no</t>
+        </is>
+      </c>
+      <c r="J435" s="2" t="inlineStr"/>
+      <c r="K435" s="2" t="inlineStr"/>
+      <c r="L435" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M435" s="2" t="inlineStr"/>
+      <c r="N435" s="2" t="inlineStr">
+        <is>
+          <t>post@bevhouse.no</t>
+        </is>
+      </c>
+      <c r="O435" s="2" t="inlineStr"/>
+      <c r="P435" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="Q435" s="2" t="inlineStr">
+        <is>
+          <t>929413393</t>
+        </is>
+      </c>
+      <c r="R435" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bevhouse/?originalSubdomain</t>
+        </is>
+      </c>
+      <c r="S435" s="2" t="inlineStr"/>
+      <c r="T435" s="2" t="inlineStr"/>
+      <c r="U435" s="2" t="inlineStr"/>
+      <c r="V435" s="2" t="inlineStr"/>
+      <c r="W435" s="2" t="inlineStr">
+        <is>
+          <t>Arnstein Nilssen</t>
+        </is>
+      </c>
+      <c r="X435" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder/ Managing Director</t>
+        </is>
+      </c>
+      <c r="Y435" s="2" t="inlineStr"/>
+      <c r="Z435" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA435" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/arnstein-nilssen-851b7731/</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="inlineStr">
+        <is>
+          <t>Bevhouse As</t>
+        </is>
+      </c>
+      <c r="B436" s="2" t="inlineStr">
+        <is>
+          <t>Bevhouse As</t>
+        </is>
+      </c>
+      <c r="C436" s="2" t="inlineStr">
+        <is>
+          <t>122451</t>
+        </is>
+      </c>
+      <c r="D436" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E436" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F436" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Oslo kommune</t>
+        </is>
+      </c>
+      <c r="G436" s="2" t="inlineStr">
+        <is>
+          <t>14 Universitetsgata</t>
+        </is>
+      </c>
+      <c r="H436" s="2" t="inlineStr">
+        <is>
+          <t>0164</t>
+        </is>
+      </c>
+      <c r="I436" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bevhouse.no</t>
+        </is>
+      </c>
+      <c r="J436" s="2" t="inlineStr"/>
+      <c r="K436" s="2" t="inlineStr"/>
+      <c r="L436" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M436" s="2" t="inlineStr"/>
+      <c r="N436" s="2" t="inlineStr">
+        <is>
+          <t>post@bevhouse.no</t>
+        </is>
+      </c>
+      <c r="O436" s="2" t="inlineStr"/>
+      <c r="P436" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="Q436" s="2" t="inlineStr">
+        <is>
+          <t>929413393</t>
+        </is>
+      </c>
+      <c r="R436" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bevhouse/?originalSubdomain</t>
+        </is>
+      </c>
+      <c r="S436" s="2" t="inlineStr"/>
+      <c r="T436" s="2" t="inlineStr"/>
+      <c r="U436" s="2" t="inlineStr"/>
+      <c r="V436" s="2" t="inlineStr"/>
+      <c r="W436" s="2" t="inlineStr">
+        <is>
+          <t>Andrée Lind</t>
+        </is>
+      </c>
+      <c r="X436" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y436" s="2" t="inlineStr"/>
+      <c r="Z436" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA436" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/andr%C3%A9e-lind-a0429612b/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
